--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -520,7 +520,7 @@
         <v>2.99</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.671</v>
@@ -564,16 +564,16 @@
         <v>0.7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6.62</v>
+        <v>6.14</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.125</v>
+        <v>0.143</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.143</v>
@@ -592,10 +592,10 @@
         <v>22</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4.73</v>
+        <v>4.59</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.409</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2</v>
@@ -1964,13 +1964,13 @@
         <v>0.913</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6.62</v>
+        <v>6.14</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Policy" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ranking Demo'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ranking Demo'!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,19 +514,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.671</v>
+        <v>0.742</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.681</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="3">
@@ -539,19 +539,19 @@
         <v>0.85</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3.24</v>
+        <v>2.14</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.667</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.619</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -564,19 +564,19 @@
         <v>0.7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6.14</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.143</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="5">
@@ -589,19 +589,19 @@
         <v>0.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4.59</v>
+        <v>4.05</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.83</v>
+        <v>4.33</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.409</v>
+        <v>0.476</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.391</v>
+        <v>0.429</v>
       </c>
     </row>
   </sheetData>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -846,25 +846,25 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -875,25 +875,25 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -904,7 +904,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -933,16 +933,16 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>3</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>4</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>5</v>
@@ -1116,16 +1116,16 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>6</v>
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1174,25 +1174,25 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1203,16 +1203,16 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>9</v>
@@ -1232,16 +1232,16 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>2</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>4</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>5</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>3</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>5</v>
@@ -1726,13 +1726,13 @@
         <v>50</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1743,25 +1743,25 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1772,16 +1772,16 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>8</v>
@@ -1801,25 +1801,25 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1830,67 +1830,38 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>not in top-10</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Q023</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>RELOC_006</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>not in top-10</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>口径：similarity_score 相同、只有排序不同 —— 该表只开 4.3 权威性排序（metadata filtering 与 query expansion 关闭），所以任何名次变化都来自权威性 tie-break。rank_delta &gt; 0 表示该证据被权威性排序往前提。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G45"/>
+  <autoFilter ref="A1:G44"/>
   <mergeCells count="1">
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1961,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.929</v>
+        <v>0.885</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6.14</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1991,13 +1962,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.827</v>
+        <v>0.931</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.912</v>
+        <v>0.874</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2015,16 +1986,16 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.92</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.823</v>
+        <v>0.931</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.915</v>
+        <v>0.874</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6.5</v>
+        <v>5.33</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2042,16 +2013,16 @@
         <v>0.2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.927</v>
+        <v>0.907</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.826</v>
+        <v>0.913</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.923</v>
+        <v>0.874</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6.88</v>
+        <v>6</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -517,16 +517,16 @@
         <v>66</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.742</v>
+        <v>0.758</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.725</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="3">
@@ -542,16 +542,16 @@
         <v>22</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.727</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="4">
@@ -567,10 +567,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.2</v>
@@ -592,10 +592,10 @@
         <v>21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.476</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -904,25 +904,25 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -933,16 +933,16 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>4</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>5</v>
@@ -1116,16 +1116,16 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>6</v>
@@ -1145,16 +1145,16 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>7</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>8</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>9</v>
@@ -1232,16 +1232,16 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>2</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>3</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>5</v>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>6</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>7</v>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>9</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>3</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>4</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>5</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>6</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>7</v>
@@ -1772,16 +1772,16 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>8</v>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>9</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1932,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.893</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.885</v>
+        <v>0.921</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1959,16 +1959,16 @@
         <v>0.01</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1986,16 +1986,16 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0.931</v>
-      </c>
       <c r="E4" s="2" t="n">
-        <v>0.874</v>
+        <v>0.894</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2013,16 +2013,16 @@
         <v>0.2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.907</v>
+        <v>0.887</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.913</v>
+        <v>0.908</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.874</v>
+        <v>0.925</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -514,19 +514,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.758</v>
+        <v>0.743</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.735</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="3">
@@ -539,19 +539,19 @@
         <v>0.85</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.727</v>
+        <v>0.759</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.773</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="4">
@@ -567,13 +567,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.17</v>
+        <v>5.42</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.167</v>
@@ -589,19 +589,19 @@
         <v>0.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.24</v>
+        <v>4.42</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.476</v>
+        <v>0.45</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.429</v>
+        <v>0.421</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2</v>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>6</v>
@@ -846,7 +846,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>XPEV_001</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>7</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>8</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>9</v>
@@ -933,7 +933,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>3</v>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>4</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1096,16 +1096,16 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1116,25 +1116,25 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
@@ -1145,16 +1145,16 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>7</v>
@@ -1174,25 +1174,25 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1215,13 +1215,13 @@
         <v>48</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -1232,16 +1232,16 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>2</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>3</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>4</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>6</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>XPEV_001</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>7</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>9</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>10</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>4</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>5</v>
@@ -1714,16 +1714,16 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>6</v>
@@ -1743,16 +1743,16 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>7</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>8</v>
@@ -1801,16 +1801,16 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>9</v>
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>10</v>
@@ -1932,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.893</v>
+        <v>0.916</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.93</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1959,16 +1959,16 @@
         <v>0.01</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.892</v>
-      </c>
       <c r="F3" s="2" t="n">
-        <v>5.17</v>
+        <v>5.42</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1986,16 +1986,16 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.893</v>
+        <v>0.8</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0.894</v>
-      </c>
       <c r="F4" s="2" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2013,16 +2013,16 @@
         <v>0.2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.887</v>
+        <v>0.785</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.908</v>
+        <v>0.905</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.925</v>
+        <v>0.921</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5.92</v>
+        <v>6.91</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -514,19 +514,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.743</v>
+        <v>0.769</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.747</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="3">
@@ -542,10 +542,10 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.759</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4</v>
@@ -1932,13 +1932,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.916</v>
+        <v>0.921</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>4.4</v>
@@ -1959,13 +1959,13 @@
         <v>0.01</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.835</v>
+        <v>0.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.919</v>
+        <v>0.925</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>5.42</v>
@@ -1986,13 +1986,13 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.91</v>
+        <v>0.916</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5.67</v>
@@ -2013,10 +2013,10 @@
         <v>0.2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.785</v>
+        <v>0.758</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.905</v>
+        <v>0.911</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.921</v>

--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -517,10 +517,10 @@
         <v>78</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.769</v>
@@ -542,16 +542,16 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.759</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.759</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="4">
@@ -567,10 +567,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.3</v>
@@ -592,10 +592,10 @@
         <v>20</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.45</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4</v>
@@ -1099,13 +1099,13 @@
         <v>51</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1125,16 +1125,16 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1157,13 +1157,13 @@
         <v>50</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>2</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>3</v>
@@ -1932,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.921</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
         <v>0.925</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1986,13 +1986,13 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.777</v>
+        <v>0.781</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.916</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5.67</v>
@@ -2016,13 +2016,13 @@
         <v>0.758</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.911</v>
+        <v>0.916</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.921</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6.91</v>
+        <v>6.55</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/task4/authority_ranking_test.xlsx
+++ b/data/evaluation/task4/authority_ranking_test.xlsx
@@ -514,16 +514,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>2.62</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>2.57</v>
-      </c>
       <c r="F2" s="2" t="n">
-        <v>0.769</v>
+        <v>0.74</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0.772</v>
@@ -539,19 +539,19 @@
         <v>0.85</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.759</v>
+        <v>0.643</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.724</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="4">
@@ -567,16 +567,16 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -589,19 +589,19 @@
         <v>0.5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4.45</v>
+        <v>4.21</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.45</v>
+        <v>0.474</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.421</v>
+        <v>0.444</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +672,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5</v>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>6</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>8</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>5</v>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1145,25 +1145,25 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1203,25 +1203,25 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>2</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>4</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>5</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>NIO_001</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>8</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>9</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>5</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>6</v>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>9</v>
@@ -1932,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.905</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1959,16 +1959,16 @@
         <v>0.01</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.925</v>
+        <v>0.907</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1986,16 +1986,16 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.781</v>
+        <v>0.786</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.916</v>
+        <v>0.898</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.922</v>
+        <v>0.924</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.67</v>
+        <v>5.11</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2013,16 +2013,16 @@
         <v>0.2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.758</v>
+        <v>0.753</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.916</v>
+        <v>0.902</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.921</v>
+        <v>0.925</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6.55</v>
+        <v>6.25</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
